--- a/tests/agent_contract/data/S8_multi_metrics.xlsx
+++ b/tests/agent_contract/data/S8_multi_metrics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,38 +413,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>客户ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>订单号</t>
+          <t>O30001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>城市</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>订单金额</t>
-        </is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>3322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>客户ID</t>
+          <t>C2301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O30001</t>
+          <t>O30002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -457,18 +470,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3604</v>
+        <v>3100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C5981</t>
+          <t>C7669</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O30002</t>
+          <t>O30003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -477,18 +490,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2094</v>
+        <v>3248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C2407</t>
+          <t>C6951</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O30003</t>
+          <t>O30004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -497,18 +510,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2082</v>
+        <v>2272</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C2686</t>
+          <t>C9383</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O30004</t>
+          <t>O30005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,18 +530,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3338</v>
+        <v>3064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C6660</t>
+          <t>C9185</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O30005</t>
+          <t>O30006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -537,18 +550,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2013</v>
+        <v>3494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C9882</t>
+          <t>C7573</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O30006</t>
+          <t>O30007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,18 +570,18 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3922</v>
+        <v>2281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C6612</t>
+          <t>C1245</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O30007</t>
+          <t>O30008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -577,18 +590,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3641</v>
+        <v>2478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C8142</t>
+          <t>C3013</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O30008</t>
+          <t>O30009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -597,18 +610,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1736</v>
+        <v>3337</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C7223</t>
+          <t>C7384</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>O30009</t>
+          <t>O30010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -617,18 +630,18 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2570</v>
+        <v>3997</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C8911</t>
+          <t>C1355</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O30010</t>
+          <t>O30011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -637,18 +650,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2590</v>
+        <v>1504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5929</t>
+          <t>C6106</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O30011</t>
+          <t>O30012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -657,18 +670,18 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1587</v>
+        <v>3011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C9354</t>
+          <t>C1334</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O30012</t>
+          <t>O30013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -677,18 +690,18 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2591</v>
+        <v>3351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1622</t>
+          <t>C2073</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O30013</t>
+          <t>O30014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -697,18 +710,18 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3394</v>
+        <v>3692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C3278</t>
+          <t>C1778</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O30014</t>
+          <t>O30015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -717,18 +730,18 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3521</v>
+        <v>3751</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C1314</t>
+          <t>C2670</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O30015</t>
+          <t>O30016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -737,18 +750,18 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1623</v>
+        <v>3187</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C1128</t>
+          <t>C5497</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O30016</t>
+          <t>O30017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -757,18 +770,18 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2230</v>
+        <v>2864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5892</t>
+          <t>C6226</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O30017</t>
+          <t>O30018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -777,18 +790,18 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2080</v>
+        <v>3537</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C1275</t>
+          <t>C7671</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O30018</t>
+          <t>O30019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -797,18 +810,18 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3854</v>
+        <v>3207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C9283</t>
+          <t>C8924</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O30019</t>
+          <t>O30020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -817,18 +830,18 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1697</v>
+        <v>1792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C8449</t>
+          <t>C3051</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O30020</t>
+          <t>O30021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -837,18 +850,18 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2843</v>
+        <v>3281</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C9331</t>
+          <t>C4007</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O30021</t>
+          <t>O30022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -857,18 +870,18 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3661</v>
+        <v>2318</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C5423</t>
+          <t>C8438</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>O30022</t>
+          <t>O30023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -877,18 +890,18 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2497</v>
+        <v>1530</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>C7322</t>
+          <t>C7108</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O30023</t>
+          <t>O30024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -897,18 +910,18 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3318</v>
+        <v>3444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C2851</t>
+          <t>C5549</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>O30024</t>
+          <t>O30025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -917,18 +930,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3748</v>
+        <v>3593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C2347</t>
+          <t>C1853</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O30025</t>
+          <t>O30026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -937,18 +950,18 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3485</v>
+        <v>2759</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C3834</t>
+          <t>C8577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>O30026</t>
+          <t>O30027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -957,18 +970,18 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3746</v>
+        <v>2220</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C9454</t>
+          <t>C5268</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>O30027</t>
+          <t>O30028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -977,18 +990,18 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2516</v>
+        <v>2378</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C6256</t>
+          <t>C6966</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>O30028</t>
+          <t>O30029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -997,18 +1010,18 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3931</v>
+        <v>2551</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C5151</t>
+          <t>C4227</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>O30029</t>
+          <t>O30030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1017,18 +1030,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3086</v>
+        <v>3532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C7133</t>
+          <t>C8838</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>O30030</t>
+          <t>O30031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1037,18 +1050,18 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3825</v>
+        <v>3986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C3771</t>
+          <t>C4270</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>O30031</t>
+          <t>O30032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1057,18 +1070,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1931</v>
+        <v>2047</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>C5699</t>
+          <t>C3287</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>O30032</t>
+          <t>O30033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1077,18 +1090,18 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3899</v>
+        <v>1861</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C2171</t>
+          <t>C4120</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O30033</t>
+          <t>O30034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1097,18 +1110,18 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2477</v>
+        <v>3784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C7770</t>
+          <t>C7389</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O30034</t>
+          <t>O30035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1117,18 +1130,18 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1753</v>
+        <v>2416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>C4392</t>
+          <t>C8350</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O30035</t>
+          <t>O30036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1137,18 +1150,18 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3034</v>
+        <v>1908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C8052</t>
+          <t>C9447</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>O30036</t>
+          <t>O30037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1157,18 +1170,18 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3973</v>
+        <v>2499</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C6891</t>
+          <t>C1417</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>O30037</t>
+          <t>O30038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1177,18 +1190,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2640</v>
+        <v>2110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C2780</t>
+          <t>C6294</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>O30038</t>
+          <t>O30039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1197,18 +1210,18 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2005</v>
+        <v>1574</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>C9853</t>
+          <t>C3083</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>O30039</t>
+          <t>O30040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1217,18 +1230,18 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1758</v>
+        <v>2154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C9431</t>
+          <t>C8363</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>O30040</t>
+          <t>O30041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1237,18 +1250,18 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1870</v>
+        <v>1562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C2338</t>
+          <t>C7682</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>O30041</t>
+          <t>O30042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1257,18 +1270,18 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1537</v>
+        <v>1501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C3007</t>
+          <t>C3591</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>O30042</t>
+          <t>O30043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1277,18 +1290,18 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1710</v>
+        <v>1500</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C6740</t>
+          <t>C1347</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>O30043</t>
+          <t>O30044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1297,18 +1310,18 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1535</v>
+        <v>1501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>C2112</t>
+          <t>C4742</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>O30044</t>
+          <t>O30045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1317,38 +1330,38 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1530</v>
+        <v>1502</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>C2903</t>
+          <t>C3446</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>O30045</t>
+          <t>O30046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1525</v>
+        <v>3723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C8933</t>
+          <t>C8287</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>O30046</t>
+          <t>O30047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1357,18 +1370,18 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3209</v>
+        <v>3626</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>C9885</t>
+          <t>C2618</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>O30047</t>
+          <t>O30048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1377,18 +1390,18 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2046</v>
+        <v>3452</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>C7463</t>
+          <t>C9672</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>O30048</t>
+          <t>O30049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1397,18 +1410,18 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3902</v>
+        <v>2344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>C4669</t>
+          <t>C5305</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>O30049</t>
+          <t>O30050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1417,18 +1430,18 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1597</v>
+        <v>2897</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>C7673</t>
+          <t>C1531</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>O30050</t>
+          <t>O30051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1437,18 +1450,18 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2468</v>
+        <v>1673</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>C9940</t>
+          <t>C4944</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>O30051</t>
+          <t>O30052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1457,18 +1470,18 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1919</v>
+        <v>2143</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>C8400</t>
+          <t>C9823</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>O30052</t>
+          <t>O30053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1477,18 +1490,18 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3856</v>
+        <v>3682</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>C9900</t>
+          <t>C6624</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>O30053</t>
+          <t>O30054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1497,18 +1510,18 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1993</v>
+        <v>2050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>C6603</t>
+          <t>C6865</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>O30054</t>
+          <t>O30055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1517,18 +1530,18 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2385</v>
+        <v>2758</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>C6943</t>
+          <t>C4364</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>O30055</t>
+          <t>O30056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1537,18 +1550,18 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2539</v>
+        <v>2954</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>C9381</t>
+          <t>C7278</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O30056</t>
+          <t>O30057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1557,18 +1570,18 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3038</v>
+        <v>3961</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>C8758</t>
+          <t>C8016</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O30057</t>
+          <t>O30058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1577,18 +1590,18 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2518</v>
+        <v>1594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>C3093</t>
+          <t>C2665</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O30058</t>
+          <t>O30059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1597,18 +1610,18 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1739</v>
+        <v>2024</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>C4613</t>
+          <t>C9765</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>O30059</t>
+          <t>O30060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1617,18 +1630,18 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2625</v>
+        <v>3277</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>C6308</t>
+          <t>C4380</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>O30060</t>
+          <t>O30061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1637,18 +1650,18 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1972</v>
+        <v>3822</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>C4201</t>
+          <t>C2328</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>O30061</t>
+          <t>O30062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1657,18 +1670,18 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1867</v>
+        <v>3863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>C6067</t>
+          <t>C9305</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>O30062</t>
+          <t>O30063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1677,18 +1690,18 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1898</v>
+        <v>3715</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>C9982</t>
+          <t>C7670</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O30063</t>
+          <t>O30064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1697,18 +1710,18 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2821</v>
+        <v>1614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C7878</t>
+          <t>C8395</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>O30064</t>
+          <t>O30065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1717,18 +1730,18 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3718</v>
+        <v>3564</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>C5487</t>
+          <t>C6295</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>O30065</t>
+          <t>O30066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1737,18 +1750,18 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2447</v>
+        <v>2063</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>C8082</t>
+          <t>C8043</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>O30066</t>
+          <t>O30067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1757,18 +1770,18 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3933</v>
+        <v>2613</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>C9420</t>
+          <t>C3927</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>O30067</t>
+          <t>O30068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1777,18 +1790,18 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1918</v>
+        <v>3384</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C2215</t>
+          <t>C3371</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>O30068</t>
+          <t>O30069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1797,18 +1810,18 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2646</v>
+        <v>1582</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>C7511</t>
+          <t>C5707</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>O30069</t>
+          <t>O30070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1817,18 +1830,18 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2520</v>
+        <v>2788</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>C3959</t>
+          <t>C8344</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>O30070</t>
+          <t>O30071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1837,18 +1850,18 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1827</v>
+        <v>2327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>C2120</t>
+          <t>C9552</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>O30071</t>
+          <t>O30072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1857,18 +1870,18 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2875</v>
+        <v>3169</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>C1753</t>
+          <t>C7703</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>O30072</t>
+          <t>O30073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1877,18 +1890,18 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2968</v>
+        <v>3064</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>C8755</t>
+          <t>C7279</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>O30073</t>
+          <t>O30074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1897,18 +1910,18 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2024</v>
+        <v>3828</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C9022</t>
+          <t>C7580</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>O30074</t>
+          <t>O30075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1917,18 +1930,18 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3170</v>
+        <v>1582</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C3888</t>
+          <t>C5993</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>O30075</t>
+          <t>O30076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1937,18 +1950,18 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2691</v>
+        <v>2211</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>C4171</t>
+          <t>C9275</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>O30076</t>
+          <t>O30077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1957,18 +1970,18 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2208</v>
+        <v>1614</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>C1883</t>
+          <t>C3990</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>O30077</t>
+          <t>O30078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1977,18 +1990,18 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1819</v>
+        <v>1510</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>C9167</t>
+          <t>C6752</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>O30078</t>
+          <t>O30079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1997,18 +2010,18 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2833</v>
+        <v>1522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>C8928</t>
+          <t>C3270</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>O30079</t>
+          <t>O30080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2017,18 +2030,18 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2937</v>
+        <v>1501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>C2204</t>
+          <t>C3126</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>O30080</t>
+          <t>O30081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2037,18 +2050,18 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1632</v>
+        <v>1500</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>C1183</t>
+          <t>C4078</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>O30081</t>
+          <t>O30082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2057,18 +2070,18 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2099</v>
+        <v>1506</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>C5876</t>
+          <t>C5896</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>O30082</t>
+          <t>O30083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2077,38 +2090,38 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2918</v>
+        <v>1500</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>C4688</t>
+          <t>C2347</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>O30083</t>
+          <t>O30084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>4425</v>
+        <v>1747</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>C4781</t>
+          <t>C3402</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>O30084</t>
+          <t>O30085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2117,18 +2130,18 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3083</v>
+        <v>1992</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>C2286</t>
+          <t>C8017</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>O30085</t>
+          <t>O30086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2137,18 +2150,18 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3406</v>
+        <v>3092</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>C2863</t>
+          <t>C9108</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>O30086</t>
+          <t>O30087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2157,18 +2170,18 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2766</v>
+        <v>3355</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>C8879</t>
+          <t>C4861</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>O30087</t>
+          <t>O30088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2177,18 +2190,18 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3519</v>
+        <v>1641</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C7137</t>
+          <t>C7494</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>O30088</t>
+          <t>O30089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2197,18 +2210,18 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2133</v>
+        <v>1962</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>C4421</t>
+          <t>C4648</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>O30089</t>
+          <t>O30090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2217,18 +2230,18 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1738</v>
+        <v>1637</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>C6022</t>
+          <t>C9806</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>O30090</t>
+          <t>O30091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2237,18 +2250,18 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3824</v>
+        <v>2633</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>C1361</t>
+          <t>C9216</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>O30091</t>
+          <t>O30092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2257,18 +2270,18 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2672</v>
+        <v>2090</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>C6358</t>
+          <t>C3676</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>O30092</t>
+          <t>O30093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2277,18 +2290,18 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2151</v>
+        <v>2159</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>C4693</t>
+          <t>C5730</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>O30093</t>
+          <t>O30094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2297,18 +2310,18 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3866</v>
+        <v>2769</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>C6699</t>
+          <t>C7404</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>O30094</t>
+          <t>O30095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2317,18 +2330,18 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2412</v>
+        <v>1909</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>C8508</t>
+          <t>C3034</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>O30095</t>
+          <t>O30096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2337,18 +2350,18 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3576</v>
+        <v>3453</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>C1820</t>
+          <t>C1942</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>O30096</t>
+          <t>O30097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2357,18 +2370,18 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2334</v>
+        <v>1551</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>C8118</t>
+          <t>C2805</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>O30097</t>
+          <t>O30098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2377,18 +2390,18 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3175</v>
+        <v>1797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>C8151</t>
+          <t>C4506</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>O30098</t>
+          <t>O30099</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2397,18 +2410,18 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2246</v>
+        <v>3756</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>C1878</t>
+          <t>C4422</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>O30099</t>
+          <t>O30100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2417,18 +2430,18 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1739</v>
+        <v>2654</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>C5975</t>
+          <t>C7773</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>O30100</t>
+          <t>O30101</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2437,18 +2450,18 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2367</v>
+        <v>3723</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>C7781</t>
+          <t>C1011</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>O30101</t>
+          <t>O30102</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2457,18 +2470,18 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1510</v>
+        <v>2038</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>C9906</t>
+          <t>C4465</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>O30102</t>
+          <t>O30103</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2477,18 +2490,18 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3144</v>
+        <v>2223</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>C1170</t>
+          <t>C7114</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>O30103</t>
+          <t>O30104</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2497,18 +2510,18 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2168</v>
+        <v>3033</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>C4716</t>
+          <t>C7462</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>O30104</t>
+          <t>O30105</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2517,18 +2530,18 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2256</v>
+        <v>2954</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>C8230</t>
+          <t>C3892</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>O30105</t>
+          <t>O30106</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2537,18 +2550,18 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1527</v>
+        <v>1616</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>C3022</t>
+          <t>C5821</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>O30106</t>
+          <t>O30107</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2557,18 +2570,18 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2003</v>
+        <v>2822</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>C3985</t>
+          <t>C9868</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>O30107</t>
+          <t>O30108</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2577,18 +2590,18 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2812</v>
+        <v>3526</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>C4769</t>
+          <t>C4221</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>O30108</t>
+          <t>O30109</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2597,18 +2610,18 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2814</v>
+        <v>1647</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>C2076</t>
+          <t>C6814</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>O30109</t>
+          <t>O30110</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2617,18 +2630,18 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1941</v>
+        <v>3956</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>C1144</t>
+          <t>C4090</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>O30110</t>
+          <t>O30111</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2637,18 +2650,18 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3611</v>
+        <v>1866</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>C3227</t>
+          <t>C6097</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>O30111</t>
+          <t>O30112</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2657,18 +2670,18 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3838</v>
+        <v>1501</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>C8740</t>
+          <t>C5389</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>O30112</t>
+          <t>O30113</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2677,18 +2690,18 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3678</v>
+        <v>2002</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>C5224</t>
+          <t>C7477</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>O30113</t>
+          <t>O30114</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2697,18 +2710,18 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2475</v>
+        <v>2504</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>C4408</t>
+          <t>C3260</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>O30114</t>
+          <t>O30115</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2717,38 +2730,38 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2711</v>
+        <v>9392</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>C8747</t>
+          <t>C2239</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>O30115</t>
+          <t>O30116</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1505</v>
+        <v>3028</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>C4359</t>
+          <t>C7748</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>O30116</t>
+          <t>O30117</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2757,18 +2770,18 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3381</v>
+        <v>2136</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>C9295</t>
+          <t>C1414</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>O30117</t>
+          <t>O30118</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2777,18 +2790,18 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2071</v>
+        <v>2550</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>C8424</t>
+          <t>C3785</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>O30118</t>
+          <t>O30119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2797,18 +2810,18 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2030</v>
+        <v>3262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>C6785</t>
+          <t>C8344</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>O30119</t>
+          <t>O30120</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2817,18 +2830,18 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2986</v>
+        <v>1889</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>C7438</t>
+          <t>C7455</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>O30120</t>
+          <t>O30121</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2837,18 +2850,18 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3562</v>
+        <v>3451</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>C6493</t>
+          <t>C6585</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>O30121</t>
+          <t>O30122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2857,18 +2870,18 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1744</v>
+        <v>2483</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>C5882</t>
+          <t>C8418</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>O30122</t>
+          <t>O30123</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2877,18 +2890,18 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1742</v>
+        <v>1944</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>C5994</t>
+          <t>C6204</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>O30123</t>
+          <t>O30124</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2897,18 +2910,18 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3493</v>
+        <v>2926</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>C5730</t>
+          <t>C2450</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>O30124</t>
+          <t>O30125</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2917,18 +2930,18 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1568</v>
+        <v>2922</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>C3630</t>
+          <t>C6603</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>O30125</t>
+          <t>O30126</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2937,18 +2950,18 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2023</v>
+        <v>1806</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>C8590</t>
+          <t>C8901</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>O30126</t>
+          <t>O30127</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2957,18 +2970,18 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3510</v>
+        <v>1503</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>C2479</t>
+          <t>C4491</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>O30127</t>
+          <t>O30128</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2977,18 +2990,18 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>C1884</t>
+          <t>C6939</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>O30128</t>
+          <t>O30129</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2997,18 +3010,18 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2796</v>
+        <v>2612</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>C6271</t>
+          <t>C3879</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>O30129</t>
+          <t>O30130</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3017,18 +3030,18 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>2216</v>
+        <v>3336</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>C5664</t>
+          <t>C5169</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>O30130</t>
+          <t>O30131</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3037,18 +3050,18 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2849</v>
+        <v>3037</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>C7449</t>
+          <t>C1920</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>O30131</t>
+          <t>O30132</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3057,18 +3070,18 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3837</v>
+        <v>1816</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>C7208</t>
+          <t>C8692</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>O30132</t>
+          <t>O30133</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3077,18 +3090,18 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3466</v>
+        <v>3911</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>C4486</t>
+          <t>C5403</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>O30133</t>
+          <t>O30134</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3097,18 +3110,18 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1947</v>
+        <v>3930</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>C1909</t>
+          <t>C6372</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>O30134</t>
+          <t>O30135</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3117,18 +3130,18 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>2641</v>
+        <v>2439</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>C1638</t>
+          <t>C6378</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>O30135</t>
+          <t>O30136</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3137,18 +3150,18 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3109</v>
+        <v>1779</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>C2592</t>
+          <t>C2027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>O30136</t>
+          <t>O30137</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3157,18 +3170,18 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3863</v>
+        <v>2065</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>C8077</t>
+          <t>C5791</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>O30137</t>
+          <t>O30138</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3177,18 +3190,18 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3168</v>
+        <v>2567</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>C9047</t>
+          <t>C4601</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>O30138</t>
+          <t>O30139</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3197,18 +3210,18 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3114</v>
+        <v>2948</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>C7585</t>
+          <t>C5565</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>O30139</t>
+          <t>O30140</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3217,18 +3230,18 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1701</v>
+        <v>2217</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>C5541</t>
+          <t>C1208</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>O30140</t>
+          <t>O30141</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3237,18 +3250,18 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2599</v>
+        <v>3270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>C5445</t>
+          <t>C9285</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>O30141</t>
+          <t>O30142</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3257,18 +3270,18 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1575</v>
+        <v>1538</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>C4672</t>
+          <t>C7946</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>O30142</t>
+          <t>O30143</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3277,38 +3290,38 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1500</v>
+        <v>2618</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>C6123</t>
+          <t>C1278</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>O30143</t>
+          <t>O30144</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1504</v>
+        <v>1982</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>C4994</t>
+          <t>C5171</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>O30144</t>
+          <t>O30145</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3317,18 +3330,18 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3562</v>
+        <v>3163</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>C2059</t>
+          <t>C5812</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>O30145</t>
+          <t>O30146</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3337,18 +3350,18 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>2818</v>
+        <v>2459</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>C1783</t>
+          <t>C7449</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>O30146</t>
+          <t>O30147</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3357,18 +3370,18 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3353</v>
+        <v>1882</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>C6466</t>
+          <t>C9350</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>O30147</t>
+          <t>O30148</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3377,18 +3390,18 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1786</v>
+        <v>3400</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>C6066</t>
+          <t>C4696</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>O30148</t>
+          <t>O30149</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3397,18 +3410,18 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1806</v>
+        <v>2314</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>C1213</t>
+          <t>C1241</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>O30149</t>
+          <t>O30150</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3417,18 +3430,18 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3581</v>
+        <v>3928</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>C4850</t>
+          <t>C2608</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>O30150</t>
+          <t>O30151</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3437,18 +3450,18 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3744</v>
+        <v>3991</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>C8838</t>
+          <t>C7383</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>O30151</t>
+          <t>O30152</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3457,18 +3470,18 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3582</v>
+        <v>1876</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>C1135</t>
+          <t>C5874</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>O30152</t>
+          <t>O30153</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3477,18 +3490,18 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1531</v>
+        <v>3342</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>C8763</t>
+          <t>C2662</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>O30153</t>
+          <t>O30154</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3497,18 +3510,18 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3652</v>
+        <v>3798</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>C5885</t>
+          <t>C9113</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>O30154</t>
+          <t>O30155</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3517,18 +3530,18 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1761</v>
+        <v>3487</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>C1866</t>
+          <t>C2835</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>O30155</t>
+          <t>O30156</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3537,18 +3550,18 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3355</v>
+        <v>1820</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>C9722</t>
+          <t>C4709</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>O30156</t>
+          <t>O30157</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3557,18 +3570,18 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3911</v>
+        <v>1766</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>C1874</t>
+          <t>C2116</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>O30157</t>
+          <t>O30158</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3577,18 +3590,18 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2598</v>
+        <v>2371</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>C8523</t>
+          <t>C9805</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>O30158</t>
+          <t>O30159</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3597,18 +3610,18 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3546</v>
+        <v>2447</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>C1940</t>
+          <t>C2612</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>O30159</t>
+          <t>O30160</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3617,18 +3630,18 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>2345</v>
+        <v>3347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>C2881</t>
+          <t>C4771</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>O30160</t>
+          <t>O30161</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3637,18 +3650,18 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>2364</v>
+        <v>2302</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>C8346</t>
+          <t>C4492</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>O30161</t>
+          <t>O30162</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3657,18 +3670,18 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>2302</v>
+        <v>3197</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>C2174</t>
+          <t>C2880</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>O30162</t>
+          <t>O30163</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3677,18 +3690,18 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>1864</v>
+        <v>1993</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>C7475</t>
+          <t>C3972</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>O30163</t>
+          <t>O30164</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3697,18 +3710,18 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>1501</v>
+        <v>1584</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>C7288</t>
+          <t>C7653</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>O30164</t>
+          <t>O30165</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3717,31 +3730,11 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1518</v>
+        <v>1551</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>C7445</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>O30165</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>C3370</t>
+          <t>C6564</t>
         </is>
       </c>
     </row>
